--- a/data/nzd0383/nzd0383.xlsx
+++ b/data/nzd0383/nzd0383.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K607"/>
+  <dimension ref="A1:K612"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23934,7 +23934,7 @@
         </is>
       </c>
       <c r="B603" t="n">
-        <v>320.58</v>
+        <v>308.95</v>
       </c>
       <c r="C603" t="n">
         <v>328.37</v>
@@ -23973,7 +23973,7 @@
         </is>
       </c>
       <c r="B604" t="n">
-        <v>325.07</v>
+        <v>308.95</v>
       </c>
       <c r="C604" t="n">
         <v>327.81</v>
@@ -24012,7 +24012,7 @@
         </is>
       </c>
       <c r="B605" t="n">
-        <v>338.42</v>
+        <v>312.43</v>
       </c>
       <c r="C605" t="n">
         <v>324.47</v>
@@ -24051,7 +24051,7 @@
         </is>
       </c>
       <c r="B606" t="n">
-        <v>338.31</v>
+        <v>312.43</v>
       </c>
       <c r="C606" t="n">
         <v>324.09</v>
@@ -24090,7 +24090,7 @@
         </is>
       </c>
       <c r="B607" t="n">
-        <v>338.31</v>
+        <v>312.43</v>
       </c>
       <c r="C607" t="n">
         <v>324.09</v>
@@ -24114,11 +24114,206 @@
         <v>330.81</v>
       </c>
       <c r="J607" t="n">
-        <v>359.16</v>
+        <v>309.45</v>
       </c>
       <c r="K607" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:12:44+00:00</t>
+        </is>
+      </c>
+      <c r="B608" t="n">
+        <v>322.96</v>
+      </c>
+      <c r="C608" t="n">
+        <v>323.38</v>
+      </c>
+      <c r="D608" t="n">
+        <v>334.29</v>
+      </c>
+      <c r="E608" t="n">
+        <v>343.19</v>
+      </c>
+      <c r="F608" t="n">
+        <v>343.65</v>
+      </c>
+      <c r="G608" t="n">
+        <v>343.55</v>
+      </c>
+      <c r="H608" t="n">
+        <v>340.12</v>
+      </c>
+      <c r="I608" t="n">
+        <v>329.49</v>
+      </c>
+      <c r="J608" t="n">
+        <v>295.7</v>
+      </c>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-02 22:18:58+00:00</t>
+        </is>
+      </c>
+      <c r="B609" t="n">
+        <v>332.17</v>
+      </c>
+      <c r="C609" t="n">
+        <v>323.62</v>
+      </c>
+      <c r="D609" t="n">
+        <v>333.63</v>
+      </c>
+      <c r="E609" t="n">
+        <v>343.25</v>
+      </c>
+      <c r="F609" t="n">
+        <v>345.26</v>
+      </c>
+      <c r="G609" t="n">
+        <v>345.74</v>
+      </c>
+      <c r="H609" t="n">
+        <v>341.41</v>
+      </c>
+      <c r="I609" t="n">
+        <v>331.43</v>
+      </c>
+      <c r="J609" t="n">
+        <v>286.38</v>
+      </c>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:12:49+00:00</t>
+        </is>
+      </c>
+      <c r="B610" t="n">
+        <v>337.7</v>
+      </c>
+      <c r="C610" t="n">
+        <v>322.79</v>
+      </c>
+      <c r="D610" t="n">
+        <v>332.89</v>
+      </c>
+      <c r="E610" t="n">
+        <v>342.54</v>
+      </c>
+      <c r="F610" t="n">
+        <v>344.62</v>
+      </c>
+      <c r="G610" t="n">
+        <v>344.82</v>
+      </c>
+      <c r="H610" t="n">
+        <v>340.73</v>
+      </c>
+      <c r="I610" t="n">
+        <v>330.61</v>
+      </c>
+      <c r="J610" t="n">
+        <v>285.03</v>
+      </c>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:13:04+00:00</t>
+        </is>
+      </c>
+      <c r="B611" t="n">
+        <v>343.29</v>
+      </c>
+      <c r="C611" t="n">
+        <v>321.8</v>
+      </c>
+      <c r="D611" t="n">
+        <v>332.45</v>
+      </c>
+      <c r="E611" t="n">
+        <v>341.66</v>
+      </c>
+      <c r="F611" t="n">
+        <v>343</v>
+      </c>
+      <c r="G611" t="n">
+        <v>343.5</v>
+      </c>
+      <c r="H611" t="n">
+        <v>340.56</v>
+      </c>
+      <c r="I611" t="n">
+        <v>331.08</v>
+      </c>
+      <c r="J611" t="n">
+        <v>288.57</v>
+      </c>
+      <c r="K611" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:19:20+00:00</t>
+        </is>
+      </c>
+      <c r="B612" t="n">
+        <v>346.84</v>
+      </c>
+      <c r="C612" t="n">
+        <v>320</v>
+      </c>
+      <c r="D612" t="n">
+        <v>330.91</v>
+      </c>
+      <c r="E612" t="n">
+        <v>340.46</v>
+      </c>
+      <c r="F612" t="n">
+        <v>342.52</v>
+      </c>
+      <c r="G612" t="n">
+        <v>342.34</v>
+      </c>
+      <c r="H612" t="n">
+        <v>340.05</v>
+      </c>
+      <c r="I612" t="n">
+        <v>329.44</v>
+      </c>
+      <c r="J612" t="n">
+        <v>288.57</v>
+      </c>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -24133,7 +24328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B617"/>
+  <dimension ref="A1:B622"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30306,6 +30501,56 @@
       </c>
       <c r="B617" t="n">
         <v>0.85</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B618" t="n">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>2026-07-02 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B619" t="n">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B620" t="n">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B621" t="n">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B622" t="n">
+        <v>0.77</v>
       </c>
     </row>
   </sheetData>
@@ -30474,28 +30719,28 @@
         <v>0.055</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3939427699099187</v>
+        <v>-0.4260742085625632</v>
       </c>
       <c r="J2" t="n">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="K2" t="n">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04253807366892626</v>
+        <v>0.04923446285601951</v>
       </c>
       <c r="M2" t="n">
-        <v>11.46164767669968</v>
+        <v>11.57285311153996</v>
       </c>
       <c r="N2" t="n">
-        <v>196.4063497272401</v>
+        <v>199.4563367517646</v>
       </c>
       <c r="O2" t="n">
-        <v>14.01450497617522</v>
+        <v>14.12290114501141</v>
       </c>
       <c r="P2" t="n">
-        <v>345.4442080216616</v>
+        <v>345.7743871390093</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -30552,28 +30797,28 @@
         <v>0.0579</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4048609731302531</v>
+        <v>-0.4123012538590633</v>
       </c>
       <c r="J3" t="n">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="K3" t="n">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2137849837144929</v>
+        <v>0.2225539619423794</v>
       </c>
       <c r="M3" t="n">
-        <v>4.841648069048158</v>
+        <v>4.835993549890609</v>
       </c>
       <c r="N3" t="n">
-        <v>33.89389878895279</v>
+        <v>33.78604492068346</v>
       </c>
       <c r="O3" t="n">
-        <v>5.821846682020473</v>
+        <v>5.812576444287289</v>
       </c>
       <c r="P3" t="n">
-        <v>337.6286800444108</v>
+        <v>337.7056395556533</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30630,28 +30875,28 @@
         <v>0.0607</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1621745412018537</v>
+        <v>-0.170733692957751</v>
       </c>
       <c r="J4" t="n">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="K4" t="n">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05316969816188366</v>
+        <v>0.05924504945930653</v>
       </c>
       <c r="M4" t="n">
-        <v>3.982159803915389</v>
+        <v>3.986907670421298</v>
       </c>
       <c r="N4" t="n">
-        <v>26.3341236909796</v>
+        <v>26.33516439957508</v>
       </c>
       <c r="O4" t="n">
-        <v>5.131678447738088</v>
+        <v>5.131779847146123</v>
       </c>
       <c r="P4" t="n">
-        <v>342.2821390530398</v>
+        <v>342.3706659828328</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30708,28 +30953,28 @@
         <v>0.0618</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2199761738292129</v>
+        <v>-0.2221023098101054</v>
       </c>
       <c r="J5" t="n">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="K5" t="n">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08797383219148946</v>
+        <v>0.091111441927064</v>
       </c>
       <c r="M5" t="n">
-        <v>4.341772138058738</v>
+        <v>4.316898419019417</v>
       </c>
       <c r="N5" t="n">
-        <v>28.20659339387771</v>
+        <v>27.99735383549057</v>
       </c>
       <c r="O5" t="n">
-        <v>5.31098798660642</v>
+        <v>5.291252577177787</v>
       </c>
       <c r="P5" t="n">
-        <v>349.39943670347</v>
+        <v>349.4214425080529</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30786,28 +31031,28 @@
         <v>0.053</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3161012933150559</v>
+        <v>-0.3172863148081572</v>
       </c>
       <c r="J6" t="n">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="K6" t="n">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1706191625603873</v>
+        <v>0.1744823398348566</v>
       </c>
       <c r="M6" t="n">
-        <v>4.140560210555773</v>
+        <v>4.11571959989871</v>
       </c>
       <c r="N6" t="n">
-        <v>27.31016336633643</v>
+        <v>27.09883947828027</v>
       </c>
       <c r="O6" t="n">
-        <v>5.225912682616926</v>
+        <v>5.205654567706185</v>
       </c>
       <c r="P6" t="n">
-        <v>353.0156858718848</v>
+        <v>353.0279529329487</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30864,28 +31109,28 @@
         <v>0.0557</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2560698617430761</v>
+        <v>-0.2613579045087517</v>
       </c>
       <c r="J7" t="n">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="K7" t="n">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1469503919509013</v>
+        <v>0.154199139828004</v>
       </c>
       <c r="M7" t="n">
-        <v>3.805533330740982</v>
+        <v>3.798133483516549</v>
       </c>
       <c r="N7" t="n">
-        <v>21.40257534615597</v>
+        <v>21.31722011917256</v>
       </c>
       <c r="O7" t="n">
-        <v>4.626291748923318</v>
+        <v>4.617057517420869</v>
       </c>
       <c r="P7" t="n">
-        <v>354.0224023115123</v>
+        <v>354.0770957852</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30942,28 +31187,28 @@
         <v>0.0546</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1375491676840498</v>
+        <v>-0.1373713141730538</v>
       </c>
       <c r="J8" t="n">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="K8" t="n">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03877948328363101</v>
+        <v>0.03943173112952836</v>
       </c>
       <c r="M8" t="n">
-        <v>4.179283990502877</v>
+        <v>4.148455620136017</v>
       </c>
       <c r="N8" t="n">
-        <v>26.3683229551443</v>
+        <v>26.15457201148883</v>
       </c>
       <c r="O8" t="n">
-        <v>5.135009537979876</v>
+        <v>5.114154085622453</v>
       </c>
       <c r="P8" t="n">
-        <v>344.1680242499421</v>
+        <v>344.1661882618376</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31020,28 +31265,28 @@
         <v>0.0518</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2078610496172893</v>
+        <v>-0.2032564909869554</v>
       </c>
       <c r="J9" t="n">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="K9" t="n">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06338211290805884</v>
+        <v>0.06182096998453523</v>
       </c>
       <c r="M9" t="n">
-        <v>4.938111260703</v>
+        <v>4.922792039739277</v>
       </c>
       <c r="N9" t="n">
-        <v>35.89942795735479</v>
+        <v>35.67071981611131</v>
       </c>
       <c r="O9" t="n">
-        <v>5.991613134820605</v>
+        <v>5.972496949862035</v>
       </c>
       <c r="P9" t="n">
-        <v>333.2623389203484</v>
+        <v>333.214728177309</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31098,28 +31343,28 @@
         <v>0.08550000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.335555482969118</v>
+        <v>-0.4026619261040949</v>
       </c>
       <c r="J10" t="n">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="K10" t="n">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01390551519320282</v>
+        <v>0.02009226021685095</v>
       </c>
       <c r="M10" t="n">
-        <v>17.2185496011504</v>
+        <v>17.31963299377993</v>
       </c>
       <c r="N10" t="n">
-        <v>448.9579710743819</v>
+        <v>449.8944612528854</v>
       </c>
       <c r="O10" t="n">
-        <v>21.1886283433917</v>
+        <v>21.21071571760098</v>
       </c>
       <c r="P10" t="n">
-        <v>327.8894635081767</v>
+        <v>328.582923071073</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -31161,7 +31406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K607"/>
+  <dimension ref="A1:K612"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65486,7 +65731,7 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>-42.12303241557473,171.328223599047</t>
+          <t>-42.12306217091628,171.32835846850543</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
@@ -65543,7 +65788,7 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>-42.12302092787305,171.3281715299618</t>
+          <t>-42.12306217091628,171.32835846850543</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
@@ -65600,7 +65845,7 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>-42.12298677165122,171.32801671442286</t>
+          <t>-42.1230532673567,171.32831811202433</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
@@ -65657,7 +65902,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>-42.12298705308908,171.32801799005577</t>
+          <t>-42.1230532673567,171.32831811202433</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
@@ -65714,7 +65959,7 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>-42.12298705308908,171.32801799005577</t>
+          <t>-42.1230532673567,171.32831811202433</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
@@ -65754,12 +65999,297 @@
       </c>
       <c r="J607" t="inlineStr">
         <is>
-          <t>-42.11771650123852,171.32860805552718</t>
+          <t>-42.11767994946152,171.32920725040196</t>
         </is>
       </c>
       <c r="K607" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:12:44+00:00</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>-42.12302632632818,171.3281959989504</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>-42.12238044815308,171.32843664249955</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>-42.12170176800348,171.32851633463412</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>-42.12102976956175,171.32859575408733</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>-42.12036894057119,171.32872457566896</t>
+        </is>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>-42.119707459643486,171.3288600181421</t>
+        </is>
+      </c>
+      <c r="H608" t="inlineStr">
+        <is>
+          <t>-42.119039361964376,171.32892190965953</t>
+        </is>
+      </c>
+      <c r="I608" t="inlineStr">
+        <is>
+          <t>-42.11836568176842,171.32905182201276</t>
+        </is>
+      </c>
+      <c r="J608" t="inlineStr">
+        <is>
+          <t>-42.117669838527746,171.32937299017988</t>
+        </is>
+      </c>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-02 22:18:58+00:00</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>-42.123002762417435,171.32808919358627</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>-42.12237988013707,171.32843384174504</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>-42.1217031315014,171.32852410436513</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>-42.12102966702711,171.32859504158645</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>-42.120366590939305,171.3287053606501</t>
+        </is>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>-42.119705501636616,171.32883366189637</t>
+        </is>
+      </c>
+      <c r="H609" t="inlineStr">
+        <is>
+          <t>-42.119039064308105,171.32890631293373</t>
+        </is>
+      </c>
+      <c r="I609" t="inlineStr">
+        <is>
+          <t>-42.11836626283561,171.32902837199848</t>
+        </is>
+      </c>
+      <c r="J609" t="inlineStr">
+        <is>
+          <t>-42.11766298501626,171.32948533158918</t>
+        </is>
+      </c>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:12:49+00:00</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>-42.12298861378978,171.32802506402055</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>-42.12238184452552,171.3284435276879</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>-42.12170466027116,171.3285328158822</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>-42.12103088035333,171.3286034728468</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>-42.12036752495485,171.32871299891832</t>
+        </is>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>-42.11970632417905,171.32884473392633</t>
+        </is>
+      </c>
+      <c r="H610" t="inlineStr">
+        <is>
+          <t>-42.11903922121246,171.3289145344636</t>
+        </is>
+      </c>
+      <c r="I610" t="inlineStr">
+        <is>
+          <t>-42.11836601723047,171.32903828386023</t>
+        </is>
+      </c>
+      <c r="J610" t="inlineStr">
+        <is>
+          <t>-42.11766199227745,171.3295016042165</t>
+        </is>
+      </c>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:13:04+00:00</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>-42.12297431161483,171.3279602386849</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>-42.12238418759022,171.32845508080132</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>-42.12170556926909,171.32853799570333</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>-42.12103238419341,171.32861392286003</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>-42.120369889179436,171.3287323332857</t>
+        </is>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>-42.11970750434678,171.3288606198829</t>
+        </is>
+      </c>
+      <c r="H611" t="inlineStr">
+        <is>
+          <t>-42.119039260438456,171.32891658984607</t>
+        </is>
+      </c>
+      <c r="I611" t="inlineStr">
+        <is>
+          <t>-42.11836615800426,171.3290326026712</t>
+        </is>
+      </c>
+      <c r="J611" t="inlineStr">
+        <is>
+          <t>-42.117664595454336,171.32945893377064</t>
+        </is>
+      </c>
+      <c r="K611" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:19:20+00:00</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>-42.12296522881949,171.3279190705537</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>-42.1223884477049,171.32847608646435</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>-42.121708750760014,171.3285561250786</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>-42.12103443488294,171.32862817287898</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>-42.120370589689806,171.32873806198745</t>
+        </is>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>-42.11970854146204,171.32887458026954</t>
+        </is>
+      </c>
+      <c r="H612" t="inlineStr">
+        <is>
+          <t>-42.11903937811622,171.32892275599352</t>
+        </is>
+      </c>
+      <c r="I612" t="inlineStr">
+        <is>
+          <t>-42.1183656667924,171.32905242639458</t>
+        </is>
+      </c>
+      <c r="J612" t="inlineStr">
+        <is>
+          <t>-42.117664595454336,171.32945893377064</t>
+        </is>
+      </c>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>

--- a/data/nzd0383/nzd0383.xlsx
+++ b/data/nzd0383/nzd0383.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K612"/>
+  <dimension ref="A1:K615"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24312,6 +24312,123 @@
         <v>288.57</v>
       </c>
       <c r="K612" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:12:59+00:00</t>
+        </is>
+      </c>
+      <c r="B613" t="n">
+        <v>350.14</v>
+      </c>
+      <c r="C613" t="n">
+        <v>319.68</v>
+      </c>
+      <c r="D613" t="n">
+        <v>331.13</v>
+      </c>
+      <c r="E613" t="n">
+        <v>340.84</v>
+      </c>
+      <c r="F613" t="n">
+        <v>342.59</v>
+      </c>
+      <c r="G613" t="n">
+        <v>341.89</v>
+      </c>
+      <c r="H613" t="n">
+        <v>339.77</v>
+      </c>
+      <c r="I613" t="n">
+        <v>329.31</v>
+      </c>
+      <c r="J613" t="n">
+        <v>288.57</v>
+      </c>
+      <c r="K613" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:19:13+00:00</t>
+        </is>
+      </c>
+      <c r="B614" t="n">
+        <v>347.99</v>
+      </c>
+      <c r="C614" t="n">
+        <v>319.86</v>
+      </c>
+      <c r="D614" t="n">
+        <v>331.34</v>
+      </c>
+      <c r="E614" t="n">
+        <v>340.79</v>
+      </c>
+      <c r="F614" t="n">
+        <v>342.55</v>
+      </c>
+      <c r="G614" t="n">
+        <v>340.72</v>
+      </c>
+      <c r="H614" t="n">
+        <v>338.6</v>
+      </c>
+      <c r="I614" t="n">
+        <v>329.55</v>
+      </c>
+      <c r="J614" t="n">
+        <v>290.32</v>
+      </c>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:13:12+00:00</t>
+        </is>
+      </c>
+      <c r="B615" t="n">
+        <v>356.16</v>
+      </c>
+      <c r="C615" t="n">
+        <v>319.28</v>
+      </c>
+      <c r="D615" t="n">
+        <v>329.04</v>
+      </c>
+      <c r="E615" t="n">
+        <v>339.37</v>
+      </c>
+      <c r="F615" t="n">
+        <v>340.08</v>
+      </c>
+      <c r="G615" t="n">
+        <v>336.12</v>
+      </c>
+      <c r="H615" t="n">
+        <v>336.2</v>
+      </c>
+      <c r="I615" t="n">
+        <v>328.07</v>
+      </c>
+      <c r="J615" t="n">
+        <v>286.61</v>
+      </c>
+      <c r="K615" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -24328,7 +24445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B622"/>
+  <dimension ref="A1:B625"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30551,6 +30668,36 @@
       </c>
       <c r="B622" t="n">
         <v>0.77</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B623" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B624" t="n">
+        <v>-0.52</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B625" t="n">
+        <v>-0.58</v>
       </c>
     </row>
   </sheetData>
@@ -30719,28 +30866,28 @@
         <v>0.055</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4260742085625632</v>
+        <v>-0.408945846389387</v>
       </c>
       <c r="J2" t="n">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="K2" t="n">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04923446285601951</v>
+        <v>0.0457250606916193</v>
       </c>
       <c r="M2" t="n">
-        <v>11.57285311153996</v>
+        <v>11.59575531988981</v>
       </c>
       <c r="N2" t="n">
-        <v>199.4563367517646</v>
+        <v>199.9534313813703</v>
       </c>
       <c r="O2" t="n">
-        <v>14.12290114501141</v>
+        <v>14.14048907857753</v>
       </c>
       <c r="P2" t="n">
-        <v>345.7743871390093</v>
+        <v>345.5967240914416</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -30797,28 +30944,28 @@
         <v>0.0579</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4123012538590633</v>
+        <v>-0.4192721782764173</v>
       </c>
       <c r="J3" t="n">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="K3" t="n">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2225539619423794</v>
+        <v>0.229268853677312</v>
       </c>
       <c r="M3" t="n">
-        <v>4.835993549890609</v>
+        <v>4.844141955459813</v>
       </c>
       <c r="N3" t="n">
-        <v>33.78604492068346</v>
+        <v>33.85540162234222</v>
       </c>
       <c r="O3" t="n">
-        <v>5.812576444287289</v>
+        <v>5.818539475017955</v>
       </c>
       <c r="P3" t="n">
-        <v>337.7056395556533</v>
+        <v>337.7779333823736</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30875,28 +31022,28 @@
         <v>0.0607</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.170733692957751</v>
+        <v>-0.1779859646919556</v>
       </c>
       <c r="J4" t="n">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="K4" t="n">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05924504945930653</v>
+        <v>0.06417582502510621</v>
       </c>
       <c r="M4" t="n">
-        <v>3.986907670421298</v>
+        <v>3.99907055110787</v>
       </c>
       <c r="N4" t="n">
-        <v>26.33516439957508</v>
+        <v>26.46502712553041</v>
       </c>
       <c r="O4" t="n">
-        <v>5.131779847146123</v>
+        <v>5.144417083162136</v>
       </c>
       <c r="P4" t="n">
-        <v>342.3706659828328</v>
+        <v>342.4458863875039</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30953,28 +31100,28 @@
         <v>0.0618</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2221023098101054</v>
+        <v>-0.2251955852680826</v>
       </c>
       <c r="J5" t="n">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="K5" t="n">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="L5" t="n">
-        <v>0.091111441927064</v>
+        <v>0.09428590130098424</v>
       </c>
       <c r="M5" t="n">
-        <v>4.316898419019417</v>
+        <v>4.311198213863823</v>
       </c>
       <c r="N5" t="n">
-        <v>27.99735383549057</v>
+        <v>27.90886315869361</v>
       </c>
       <c r="O5" t="n">
-        <v>5.291252577177787</v>
+        <v>5.282883981188079</v>
       </c>
       <c r="P5" t="n">
-        <v>349.4214425080529</v>
+        <v>349.4535286922372</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31031,28 +31178,28 @@
         <v>0.053</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3172863148081572</v>
+        <v>-0.3200130885836527</v>
       </c>
       <c r="J6" t="n">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="K6" t="n">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1744823398348566</v>
+        <v>0.1784582892901639</v>
       </c>
       <c r="M6" t="n">
-        <v>4.11571959989871</v>
+        <v>4.109995849350758</v>
       </c>
       <c r="N6" t="n">
-        <v>27.09883947828027</v>
+        <v>27.00886944624706</v>
       </c>
       <c r="O6" t="n">
-        <v>5.205654567706185</v>
+        <v>5.19700581549098</v>
       </c>
       <c r="P6" t="n">
-        <v>353.0279529329487</v>
+        <v>353.0562437483214</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31109,28 +31256,28 @@
         <v>0.0557</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2613579045087517</v>
+        <v>-0.2688040277248394</v>
       </c>
       <c r="J7" t="n">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="K7" t="n">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="L7" t="n">
-        <v>0.154199139828004</v>
+        <v>0.1613878768155079</v>
       </c>
       <c r="M7" t="n">
-        <v>3.798133483516549</v>
+        <v>3.813083730540456</v>
       </c>
       <c r="N7" t="n">
-        <v>21.31722011917256</v>
+        <v>21.50996987900509</v>
       </c>
       <c r="O7" t="n">
-        <v>4.617057517420869</v>
+        <v>4.637884202845635</v>
       </c>
       <c r="P7" t="n">
-        <v>354.0770957852</v>
+        <v>354.1543438858101</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31187,28 +31334,28 @@
         <v>0.0546</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1373713141730538</v>
+        <v>-0.1396409647761845</v>
       </c>
       <c r="J8" t="n">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="K8" t="n">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03943173112952836</v>
+        <v>0.04110211683875109</v>
       </c>
       <c r="M8" t="n">
-        <v>4.148455620136017</v>
+        <v>4.139038076688704</v>
       </c>
       <c r="N8" t="n">
-        <v>26.15457201148883</v>
+        <v>26.06224854194941</v>
       </c>
       <c r="O8" t="n">
-        <v>5.114154085622453</v>
+        <v>5.105119836198697</v>
       </c>
       <c r="P8" t="n">
-        <v>344.1661882618376</v>
+        <v>344.189742598693</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31265,28 +31412,28 @@
         <v>0.0518</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2032564909869554</v>
+        <v>-0.2020140669727787</v>
       </c>
       <c r="J9" t="n">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="K9" t="n">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06182096998453523</v>
+        <v>0.06177964083973242</v>
       </c>
       <c r="M9" t="n">
-        <v>4.922792039739277</v>
+        <v>4.905443906392764</v>
       </c>
       <c r="N9" t="n">
-        <v>35.67071981611131</v>
+        <v>35.50591654434842</v>
       </c>
       <c r="O9" t="n">
-        <v>5.972496949862035</v>
+        <v>5.958684128593193</v>
       </c>
       <c r="P9" t="n">
-        <v>333.214728177309</v>
+        <v>333.2018503810951</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31343,28 +31490,28 @@
         <v>0.08550000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4026619261040949</v>
+        <v>-0.4318433506898416</v>
       </c>
       <c r="J10" t="n">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="K10" t="n">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02009226021685095</v>
+        <v>0.0231006290791822</v>
       </c>
       <c r="M10" t="n">
-        <v>17.31963299377993</v>
+        <v>17.39911714710427</v>
       </c>
       <c r="N10" t="n">
-        <v>449.8944612528854</v>
+        <v>451.8107160441418</v>
       </c>
       <c r="O10" t="n">
-        <v>21.21071571760098</v>
+        <v>21.25583957514127</v>
       </c>
       <c r="P10" t="n">
-        <v>328.582923071073</v>
+        <v>328.8855598426838</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -31406,7 +31553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K612"/>
+  <dimension ref="A1:K615"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66293,6 +66440,177 @@
         </is>
       </c>
     </row>
+    <row r="613">
+      <c r="A613" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:12:59+00:00</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>-42.12295678564454,171.32788080159753</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>-42.122389205058234,171.32847982080474</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>-42.12170829626149,171.3285535351677</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>-42.1210337854981,171.32862366037287</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>-42.120370487532064,171.32873722655177</t>
+        </is>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>-42.119708943790805,171.32887999593692</t>
+        </is>
+      </c>
+      <c r="H613" t="inlineStr">
+        <is>
+          <t>-42.119039442723476,171.3289261413294</t>
+        </is>
+      </c>
+      <c r="I613" t="inlineStr">
+        <is>
+          <t>-42.11836562785472,171.32905399778727</t>
+        </is>
+      </c>
+      <c r="J613" t="inlineStr">
+        <is>
+          <t>-42.117664595454336,171.32945893377064</t>
+        </is>
+      </c>
+      <c r="K613" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:19:13+00:00</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>-42.12296228650239,171.32790573440107</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>-42.122388779047,171.32847772023828</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>-42.12170786242193,171.3285510629801</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>-42.121033870943485,171.32862425412367</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>-42.1203705459079,171.3287377039436</t>
+        </is>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>-42.11970998984436,171.3288940766724</t>
+        </is>
+      </c>
+      <c r="H614" t="inlineStr">
+        <is>
+          <t>-42.11903971268847,171.3289402871972</t>
+        </is>
+      </c>
+      <c r="I614" t="inlineStr">
+        <is>
+          <t>-42.118365699739634,171.3290510967546</t>
+        </is>
+      </c>
+      <c r="J614" t="inlineStr">
+        <is>
+          <t>-42.117665882329675,171.32943783962253</t>
+        </is>
+      </c>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:13:12+00:00</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>-42.122941383214155,171.32781098977136</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>-42.12239015174972,171.3284844887304</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>-42.121712613995186,171.32857813932253</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>-42.12103629759104,171.32864111664702</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>-42.12037415061311,171.32876718289012</t>
+        </is>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>-42.119714102516866,171.32894943683414</t>
+        </is>
+      </c>
+      <c r="H615" t="inlineStr">
+        <is>
+          <t>-42.119040266457326,171.32896930436257</t>
+        </is>
+      </c>
+      <c r="I615" t="inlineStr">
+        <is>
+          <t>-42.11836525644816,171.32906898645604</t>
+        </is>
+      </c>
+      <c r="J615" t="inlineStr">
+        <is>
+          <t>-42.11766315414932,171.3294825592156</t>
+        </is>
+      </c>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0383/nzd0383.xlsx
+++ b/data/nzd0383/nzd0383.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K615"/>
+  <dimension ref="A1:K616"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24431,6 +24431,45 @@
       <c r="K615" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:13:16+00:00</t>
+        </is>
+      </c>
+      <c r="B616" t="n">
+        <v>356.16</v>
+      </c>
+      <c r="C616" t="n">
+        <v>319.28</v>
+      </c>
+      <c r="D616" t="n">
+        <v>329.04</v>
+      </c>
+      <c r="E616" t="n">
+        <v>339.37</v>
+      </c>
+      <c r="F616" t="n">
+        <v>340.08</v>
+      </c>
+      <c r="G616" t="n">
+        <v>336.12</v>
+      </c>
+      <c r="H616" t="n">
+        <v>336.92</v>
+      </c>
+      <c r="I616" t="n">
+        <v>327.56</v>
+      </c>
+      <c r="J616" t="n">
+        <v>286.61</v>
+      </c>
+      <c r="K616" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -24445,7 +24484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B625"/>
+  <dimension ref="A1:B626"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30698,6 +30737,16 @@
       </c>
       <c r="B625" t="n">
         <v>-0.58</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B626" t="n">
+        <v>0.44</v>
       </c>
     </row>
   </sheetData>
@@ -30866,28 +30915,28 @@
         <v>0.055</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.408945846389387</v>
+        <v>-0.4017208100437885</v>
       </c>
       <c r="J2" t="n">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="K2" t="n">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0457250606916193</v>
+        <v>0.04420142367473467</v>
       </c>
       <c r="M2" t="n">
-        <v>11.59575531988981</v>
+        <v>11.61041353449378</v>
       </c>
       <c r="N2" t="n">
-        <v>199.9534313813703</v>
+        <v>200.3854203239729</v>
       </c>
       <c r="O2" t="n">
-        <v>14.14048907857753</v>
+        <v>14.15575573129082</v>
       </c>
       <c r="P2" t="n">
-        <v>345.5967240914416</v>
+        <v>345.5214885144101</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -30944,28 +30993,28 @@
         <v>0.0579</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4192721782764173</v>
+        <v>-0.4216598335481423</v>
       </c>
       <c r="J3" t="n">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="K3" t="n">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="L3" t="n">
-        <v>0.229268853677312</v>
+        <v>0.2315501245407443</v>
       </c>
       <c r="M3" t="n">
-        <v>4.844141955459813</v>
+        <v>4.847087154442494</v>
       </c>
       <c r="N3" t="n">
-        <v>33.85540162234222</v>
+        <v>33.88303702511283</v>
       </c>
       <c r="O3" t="n">
-        <v>5.818539475017955</v>
+        <v>5.82091376204053</v>
       </c>
       <c r="P3" t="n">
-        <v>337.7779333823736</v>
+        <v>337.8027964575926</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31022,28 +31071,28 @@
         <v>0.0607</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1779859646919556</v>
+        <v>-0.1808521613298114</v>
       </c>
       <c r="J4" t="n">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="K4" t="n">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="L4" t="n">
-        <v>0.06417582502510621</v>
+        <v>0.06608777859400794</v>
       </c>
       <c r="M4" t="n">
-        <v>3.99907055110787</v>
+        <v>4.005189303148259</v>
       </c>
       <c r="N4" t="n">
-        <v>26.46502712553041</v>
+        <v>26.54114470955187</v>
       </c>
       <c r="O4" t="n">
-        <v>5.144417083162136</v>
+        <v>5.151809847961381</v>
       </c>
       <c r="P4" t="n">
-        <v>342.4458863875039</v>
+        <v>342.4757325983214</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31100,28 +31149,28 @@
         <v>0.0618</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2251955852680826</v>
+        <v>-0.2265266393750998</v>
       </c>
       <c r="J5" t="n">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="K5" t="n">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09428590130098424</v>
+        <v>0.09555876361780802</v>
       </c>
       <c r="M5" t="n">
-        <v>4.311198213863823</v>
+        <v>4.31076448398275</v>
       </c>
       <c r="N5" t="n">
-        <v>27.90886315869361</v>
+        <v>27.88917939746483</v>
       </c>
       <c r="O5" t="n">
-        <v>5.282883981188079</v>
+        <v>5.281020677621403</v>
       </c>
       <c r="P5" t="n">
-        <v>349.4535286922372</v>
+        <v>349.4673891932798</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31178,28 +31227,28 @@
         <v>0.053</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3200130885836527</v>
+        <v>-0.3214535638181283</v>
       </c>
       <c r="J6" t="n">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="K6" t="n">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1784582892901639</v>
+        <v>0.1801975708919352</v>
       </c>
       <c r="M6" t="n">
-        <v>4.109995849350758</v>
+        <v>4.110854987439231</v>
       </c>
       <c r="N6" t="n">
-        <v>27.00886944624706</v>
+        <v>26.99504757619276</v>
       </c>
       <c r="O6" t="n">
-        <v>5.19700581549098</v>
+        <v>5.195675853649144</v>
       </c>
       <c r="P6" t="n">
-        <v>353.0562437483214</v>
+        <v>353.071243670852</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31256,28 +31305,28 @@
         <v>0.0557</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2688040277248394</v>
+        <v>-0.2723955946912581</v>
       </c>
       <c r="J7" t="n">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="K7" t="n">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1613878768155079</v>
+        <v>0.164363271351091</v>
       </c>
       <c r="M7" t="n">
-        <v>3.813083730540456</v>
+        <v>3.823072399558867</v>
       </c>
       <c r="N7" t="n">
-        <v>21.50996987900509</v>
+        <v>21.66208431188335</v>
       </c>
       <c r="O7" t="n">
-        <v>4.637884202845635</v>
+        <v>4.65425443136528</v>
       </c>
       <c r="P7" t="n">
-        <v>354.1543438858101</v>
+        <v>354.1917435057206</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31334,28 +31383,28 @@
         <v>0.0546</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1396409647761845</v>
+        <v>-0.1408048171100632</v>
       </c>
       <c r="J8" t="n">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="K8" t="n">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04110211683875109</v>
+        <v>0.04188948720483843</v>
       </c>
       <c r="M8" t="n">
-        <v>4.139038076688704</v>
+        <v>4.13784489433318</v>
       </c>
       <c r="N8" t="n">
-        <v>26.06224854194941</v>
+        <v>26.03951709417623</v>
       </c>
       <c r="O8" t="n">
-        <v>5.105119836198697</v>
+        <v>5.102893012221227</v>
       </c>
       <c r="P8" t="n">
-        <v>344.189742598693</v>
+        <v>344.2018619981992</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31412,28 +31461,28 @@
         <v>0.0518</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2020140669727787</v>
+        <v>-0.2020709623306796</v>
       </c>
       <c r="J9" t="n">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="K9" t="n">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06177964083973242</v>
+        <v>0.06204175911091681</v>
       </c>
       <c r="M9" t="n">
-        <v>4.905443906392764</v>
+        <v>4.89771494540361</v>
       </c>
       <c r="N9" t="n">
-        <v>35.50591654434842</v>
+        <v>35.44823029679038</v>
       </c>
       <c r="O9" t="n">
-        <v>5.958684128593193</v>
+        <v>5.953841641897303</v>
       </c>
       <c r="P9" t="n">
-        <v>333.2018503810951</v>
+        <v>333.202442842486</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31490,28 +31539,28 @@
         <v>0.08550000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4318433506898416</v>
+        <v>-0.4420539348454883</v>
       </c>
       <c r="J10" t="n">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="K10" t="n">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0231006290791822</v>
+        <v>0.02419348164041824</v>
       </c>
       <c r="M10" t="n">
-        <v>17.39911714710427</v>
+        <v>17.42815734291849</v>
       </c>
       <c r="N10" t="n">
-        <v>451.8107160441418</v>
+        <v>452.5881759220363</v>
       </c>
       <c r="O10" t="n">
-        <v>21.25583957514127</v>
+        <v>21.27411986245345</v>
       </c>
       <c r="P10" t="n">
-        <v>328.8855598426838</v>
+        <v>328.991884455327</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -31553,7 +31602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K615"/>
+  <dimension ref="A1:K616"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66611,6 +66660,63 @@
         </is>
       </c>
     </row>
+    <row r="616">
+      <c r="A616" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:13:16+00:00</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>-42.122941383214155,171.32781098977136</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>-42.12239015174972,171.3284844887304</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>-42.121712613995186,171.32857813932253</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>-42.12103629759104,171.32864111664702</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>-42.12037415061311,171.32876718289012</t>
+        </is>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>-42.119714102516866,171.32894943683414</t>
+        </is>
+      </c>
+      <c r="H616" t="inlineStr">
+        <is>
+          <t>-42.119040100327425,171.32896059921288</t>
+        </is>
+      </c>
+      <c r="I616" t="inlineStr">
+        <is>
+          <t>-42.11836510369166,171.32907515115042</t>
+        </is>
+      </c>
+      <c r="J616" t="inlineStr">
+        <is>
+          <t>-42.11766315414932,171.3294825592156</t>
+        </is>
+      </c>
+      <c r="K616" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
